--- a/products/AZ3002/AZ3002 - PO#20158141 - 20250316.xlsx
+++ b/products/AZ3002/AZ3002 - PO#20158141 - 20250316.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12300"/>
+    <workbookView windowWidth="22192" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="测试数据" sheetId="11" r:id="rId1"/>
@@ -26,6 +26,10 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="69">
   <si>
@@ -245,14 +249,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="8">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="182" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="183" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="180" formatCode="dd\-mmm\-yy"/>
+    <numFmt numFmtId="181" formatCode="0.0"/>
   </numFmts>
   <fonts count="58">
     <font>
@@ -1265,16 +1269,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1575,11 +1579,11 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="134"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="135"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="135" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="135" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="134" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1640,28 +1644,25 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="125" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="125" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1680,7 +1681,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="125" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1691,7 +1692,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1707,28 +1708,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="9" fillId="2" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="13" fillId="0" borderId="1" xfId="124" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="1" xfId="124" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="0" xfId="125" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="15" fillId="0" borderId="0" xfId="125" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="134" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1738,15 +1739,15 @@
     <xf numFmtId="58" fontId="5" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="2" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="3" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="3" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="4" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="4" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1754,15 +1755,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="125" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="5" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="5" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="6" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="6" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="7" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="7" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1777,7 +1778,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="125" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="4" borderId="1" xfId="125" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1803,7 +1804,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -2038,34 +2039,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
+      <xdr:colOff>10160</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>37465</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>271877</xdr:colOff>
+      <xdr:colOff>600710</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>225425</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="ID_3CC97CAB80B54EEBA04231B2F067BC79" descr="Thiết kế chưa có tên (1)"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
-        <a:srcRect l="1143"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="161925" y="57150"/>
-          <a:ext cx="2042795" cy="676275"/>
+          <a:off x="10160" y="37465"/>
+          <a:ext cx="2670810" cy="702310"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2365,30 +2365,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.2857142857143" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.7047619047619" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.42857142857143" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.85714285714286" style="2" customWidth="1"/>
-    <col min="5" max="6" width="7.42857142857143" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.283185840708" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.7079646017699" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.42477876106195" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.85840707964602" style="2" customWidth="1"/>
+    <col min="5" max="6" width="7.42477876106195" style="2" customWidth="1"/>
     <col min="7" max="7" width="10" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.42857142857143" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.28571428571429" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.42857142857143" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.28571428571429" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.42857142857143" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.7047619047619" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.42477876106195" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.28318584070797" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.42477876106195" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.28318584070797" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.42477876106195" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.70796460176991" style="3" customWidth="1"/>
     <col min="14" max="14" width="7" style="3" customWidth="1"/>
-    <col min="15" max="15" width="6.85714285714286" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.28571428571429" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.42857142857143" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.7047619047619" style="2" customWidth="1"/>
-    <col min="19" max="19" width="5.85714285714286" style="2" customWidth="1"/>
-    <col min="20" max="20" width="6.56190476190476" style="2" customWidth="1"/>
-    <col min="21" max="21" width="6.42857142857143" style="2" customWidth="1"/>
-    <col min="22" max="22" width="6.28571428571429" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.56190476190476" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.85840707964602" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.28318584070797" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7.42477876106195" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.70796460176991" style="2" customWidth="1"/>
+    <col min="19" max="19" width="5.85840707964602" style="2" customWidth="1"/>
+    <col min="20" max="20" width="6.55752212389381" style="2" customWidth="1"/>
+    <col min="21" max="21" width="6.42477876106195" style="2" customWidth="1"/>
+    <col min="22" max="22" width="6.28318584070797" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7.55752212389381" style="2" customWidth="1"/>
     <col min="24" max="24" width="7" style="2" hidden="1" customWidth="1"/>
     <col min="25" max="16384" width="9" style="2"/>
   </cols>
@@ -2415,14 +2415,14 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51" t="s">
+      <c r="U1" s="50"/>
+      <c r="V1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="W1" s="51"/>
+      <c r="W1" s="50"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:23">
       <c r="A2" s="4"/>
@@ -2444,14 +2444,14 @@
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
       <c r="S2" s="5"/>
-      <c r="T2" s="52" t="s">
+      <c r="T2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52" t="s">
+      <c r="U2" s="51"/>
+      <c r="V2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="52"/>
+      <c r="W2" s="51"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:23">
       <c r="A3" s="4"/>
@@ -2473,14 +2473,14 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
-      <c r="T3" s="52" t="s">
+      <c r="T3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="52"/>
-      <c r="V3" s="72" t="s">
+      <c r="U3" s="51"/>
+      <c r="V3" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="W3" s="53"/>
+      <c r="W3" s="52"/>
     </row>
     <row r="4" ht="15.75" spans="1:24">
       <c r="A4" s="6" t="s">
@@ -2508,23 +2508,23 @@
         <v>10</v>
       </c>
       <c r="O4" s="8"/>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="Q4" s="37"/>
+      <c r="Q4" s="36"/>
       <c r="R4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="S4" s="7"/>
-      <c r="T4" s="54" t="s">
+      <c r="T4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="57"/>
+      <c r="U4" s="54"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="55"/>
+      <c r="X4" s="56"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" ht="15.75" spans="1:24">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -2542,21 +2542,21 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="36"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="58" t="s">
+      <c r="O5" s="35"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="S5" s="58"/>
-      <c r="T5" s="59"/>
-      <c r="U5" s="60"/>
-      <c r="V5" s="60"/>
-      <c r="W5" s="61"/>
-      <c r="X5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="60"/>
+      <c r="X5" s="56"/>
     </row>
     <row r="6" ht="25.5" customHeight="1" spans="1:25">
       <c r="A6" s="11" t="s">
@@ -2581,35 +2581,35 @@
         <v>23</v>
       </c>
       <c r="H6" s="12"/>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="K6" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="39" t="s">
+      <c r="M6" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="39"/>
+      <c r="N6" s="38"/>
       <c r="O6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="40" t="s">
+      <c r="P6" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="40" t="s">
+      <c r="Q6" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="40" t="s">
+      <c r="R6" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="S6" s="40" t="s">
+      <c r="S6" s="39" t="s">
         <v>33</v>
       </c>
       <c r="T6" s="12" t="s">
@@ -2625,9 +2625,9 @@
         <v>37</v>
       </c>
       <c r="X6" s="12"/>
-      <c r="Y6" s="70"/>
+      <c r="Y6" s="69"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:25">
+    <row r="7" customHeight="1" spans="1:25">
       <c r="A7" s="11" t="s">
         <v>38</v>
       </c>
@@ -2644,29 +2644,29 @@
       <c r="H7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="39" t="s">
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="39" t="s">
+      <c r="N7" s="38" t="s">
         <v>41</v>
       </c>
       <c r="O7" s="12"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
-      <c r="Y7" s="70"/>
+      <c r="Y7" s="69"/>
     </row>
-    <row r="8" ht="24" spans="1:25">
+    <row r="8" ht="23.25" spans="1:25">
       <c r="A8" s="11"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2679,23 +2679,23 @@
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
       <c r="O8" s="12"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="12"/>
-      <c r="Y8" s="70"/>
+      <c r="Y8" s="69"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:25">
       <c r="A9" s="15" t="s">
@@ -2722,22 +2722,22 @@
       <c r="H9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J9" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="42" t="s">
+      <c r="L9" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="43" t="s">
+      <c r="M9" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="43" t="s">
+      <c r="N9" s="42" t="s">
         <v>56</v>
       </c>
       <c r="O9" s="16" t="s">
@@ -2767,10 +2767,10 @@
       <c r="W9" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="X9" s="62" t="s">
+      <c r="X9" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="Y9" s="70"/>
+      <c r="Y9" s="69"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:25">
       <c r="A10" s="18"/>
@@ -2781,12 +2781,12 @@
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
       <c r="O10" s="16"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
@@ -2796,10 +2796,10 @@
       <c r="U10" s="16"/>
       <c r="V10" s="16"/>
       <c r="W10" s="16"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="70"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="69"/>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" ht="15.75" spans="1:25">
       <c r="A11" s="19" t="s">
         <v>58</v>
       </c>
@@ -2824,16 +2824,16 @@
       <c r="H11" s="22">
         <v>133.54</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>3325</v>
       </c>
-      <c r="J11" s="44">
+      <c r="J11" s="43">
         <v>932</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="43">
         <v>1847</v>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="43">
         <v>602</v>
       </c>
       <c r="M11" s="22">
@@ -2869,10 +2869,10 @@
       <c r="W11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="X11" s="63"/>
-      <c r="Y11" s="71"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="70"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" ht="15.75" spans="1:25">
       <c r="A12" s="19" t="s">
         <v>60</v>
       </c>
@@ -2897,16 +2897,16 @@
       <c r="H12" s="22">
         <v>130.14</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>3326</v>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="43">
         <v>991</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="43">
         <v>1865</v>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="43">
         <v>534</v>
       </c>
       <c r="M12" s="22">
@@ -2942,10 +2942,10 @@
       <c r="W12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="X12" s="63"/>
-      <c r="Y12" s="70"/>
+      <c r="X12" s="62"/>
+      <c r="Y12" s="69"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" ht="15.75" spans="1:25">
       <c r="A13" s="19" t="s">
         <v>61</v>
       </c>
@@ -2970,16 +2970,16 @@
       <c r="H13" s="22">
         <v>131.83</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>3320</v>
       </c>
-      <c r="J13" s="44">
+      <c r="J13" s="43">
         <v>909</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="43">
         <v>1911</v>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="43">
         <v>595</v>
       </c>
       <c r="M13" s="22">
@@ -3015,10 +3015,10 @@
       <c r="W13" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="X13" s="63"/>
-      <c r="Y13" s="70"/>
+      <c r="X13" s="62"/>
+      <c r="Y13" s="69"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" ht="15.75" spans="1:25">
       <c r="A14" s="19" t="s">
         <v>62</v>
       </c>
@@ -3043,16 +3043,16 @@
       <c r="H14" s="22">
         <v>129.47</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>3274</v>
       </c>
-      <c r="J14" s="44">
+      <c r="J14" s="43">
         <v>941</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="43">
         <v>1843</v>
       </c>
-      <c r="L14" s="44">
+      <c r="L14" s="43">
         <v>569</v>
       </c>
       <c r="M14" s="22">
@@ -3088,10 +3088,10 @@
       <c r="W14" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="X14" s="63"/>
-      <c r="Y14" s="70"/>
+      <c r="X14" s="62"/>
+      <c r="Y14" s="69"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" ht="15.75" spans="1:25">
       <c r="A15" s="19" t="s">
         <v>63</v>
       </c>
@@ -3116,16 +3116,16 @@
       <c r="H15" s="22">
         <v>130.04</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>3328</v>
       </c>
-      <c r="J15" s="44">
+      <c r="J15" s="43">
         <v>905</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="43">
         <v>1923</v>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="43">
         <v>530</v>
       </c>
       <c r="M15" s="22">
@@ -3161,10 +3161,10 @@
       <c r="W15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="X15" s="63"/>
-      <c r="Y15" s="70"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="69"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" ht="15.75" spans="1:24">
       <c r="A16" s="19">
         <v>6</v>
       </c>
@@ -3175,168 +3175,168 @@
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
-      <c r="I16" s="45"/>
+      <c r="I16" s="44"/>
       <c r="J16" s="22"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="46"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="45"/>
       <c r="P16" s="24"/>
       <c r="Q16" s="24"/>
-      <c r="R16" s="64"/>
-      <c r="S16" s="64"/>
+      <c r="R16" s="63"/>
+      <c r="S16" s="63"/>
       <c r="T16" s="24"/>
-      <c r="U16" s="65"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="65"/>
-      <c r="X16" s="63"/>
+      <c r="U16" s="64"/>
+      <c r="V16" s="64"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="62"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" ht="15.75" spans="1:24">
       <c r="A17" s="19">
         <v>7</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="23"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="28"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="27"/>
       <c r="P17" s="24"/>
       <c r="Q17" s="24"/>
-      <c r="R17" s="64"/>
-      <c r="S17" s="64"/>
+      <c r="R17" s="63"/>
+      <c r="S17" s="63"/>
       <c r="T17" s="24"/>
-      <c r="U17" s="65"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="65"/>
-      <c r="X17" s="63"/>
+      <c r="U17" s="64"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="62"/>
     </row>
-    <row r="18" spans="1:24">
-      <c r="A18" s="26">
+    <row r="18" ht="15.75" spans="1:24">
+      <c r="A18" s="25">
         <v>8</v>
       </c>
-      <c r="B18" s="27"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="23"/>
       <c r="D18" s="24"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="28"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="27"/>
       <c r="P18" s="24"/>
       <c r="Q18" s="24"/>
-      <c r="R18" s="64"/>
-      <c r="S18" s="64"/>
+      <c r="R18" s="63"/>
+      <c r="S18" s="63"/>
       <c r="T18" s="24"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="63"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="62"/>
     </row>
-    <row r="19" spans="1:24">
-      <c r="A19" s="26">
+    <row r="19" ht="15.75" spans="1:24">
+      <c r="A19" s="25">
         <v>9</v>
       </c>
-      <c r="B19" s="27"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="23"/>
       <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="47"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="46"/>
       <c r="Q19" s="24"/>
-      <c r="R19" s="64"/>
-      <c r="S19" s="64"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="63"/>
       <c r="T19" s="24"/>
-      <c r="U19" s="65"/>
-      <c r="V19" s="65"/>
-      <c r="W19" s="65"/>
-      <c r="X19" s="63"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="62"/>
     </row>
-    <row r="20" spans="1:24">
-      <c r="A20" s="26">
+    <row r="20" ht="15.75" spans="1:24">
+      <c r="A20" s="25">
         <v>10</v>
       </c>
-      <c r="B20" s="27"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="23"/>
       <c r="D20" s="24"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="47"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="46"/>
       <c r="Q20" s="24"/>
-      <c r="R20" s="64"/>
-      <c r="S20" s="64"/>
+      <c r="R20" s="63"/>
+      <c r="S20" s="63"/>
       <c r="T20" s="24"/>
-      <c r="U20" s="65"/>
-      <c r="V20" s="65"/>
-      <c r="W20" s="65"/>
-      <c r="X20" s="63"/>
+      <c r="U20" s="64"/>
+      <c r="V20" s="64"/>
+      <c r="W20" s="64"/>
+      <c r="X20" s="62"/>
     </row>
-    <row r="21" spans="1:24">
-      <c r="A21" s="26">
+    <row r="21" ht="15.75" spans="1:24">
+      <c r="A21" s="25">
         <v>11</v>
       </c>
-      <c r="B21" s="27"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="23"/>
       <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="47"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="46"/>
       <c r="Q21" s="24"/>
-      <c r="R21" s="64"/>
-      <c r="S21" s="64"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
       <c r="T21" s="24"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="63"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="64"/>
+      <c r="X21" s="62"/>
     </row>
-    <row r="22" spans="1:24">
-      <c r="A22" s="26">
+    <row r="22" ht="15.75" spans="1:24">
+      <c r="A22" s="25">
         <v>12</v>
       </c>
-      <c r="B22" s="27"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="23"/>
       <c r="D22" s="24"/>
       <c r="E22" s="22"/>
@@ -3349,467 +3349,467 @@
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="47"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="46"/>
       <c r="Q22" s="24"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
+      <c r="R22" s="63"/>
+      <c r="S22" s="63"/>
       <c r="T22" s="24"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="63"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="62"/>
     </row>
-    <row r="23" spans="1:24">
-      <c r="A23" s="26">
+    <row r="23" ht="15.75" spans="1:24">
+      <c r="A23" s="25">
         <v>13</v>
       </c>
-      <c r="B23" s="27"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="23"/>
       <c r="D23" s="24"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="47"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="46"/>
       <c r="Q23" s="24"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
+      <c r="R23" s="63"/>
+      <c r="S23" s="63"/>
       <c r="T23" s="24"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="63"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="62"/>
     </row>
-    <row r="24" spans="1:24">
-      <c r="A24" s="26">
+    <row r="24" ht="15.75" spans="1:24">
+      <c r="A24" s="25">
         <v>14</v>
       </c>
-      <c r="B24" s="27"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="23"/>
       <c r="D24" s="24"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
       <c r="T24" s="24"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="65"/>
-      <c r="X24" s="63"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="26"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="62"/>
     </row>
-    <row r="25" spans="1:24">
-      <c r="A25" s="26">
+    <row r="25" ht="15.75" spans="1:24">
+      <c r="A25" s="25">
         <v>15</v>
       </c>
-      <c r="B25" s="27"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="23"/>
       <c r="D25" s="24"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
       <c r="T25" s="24"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="65"/>
-      <c r="X25" s="63"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="26"/>
+      <c r="W25" s="64"/>
+      <c r="X25" s="62"/>
     </row>
-    <row r="26" spans="1:24">
-      <c r="A26" s="26">
+    <row r="26" ht="15.75" spans="1:24">
+      <c r="A26" s="25">
         <v>16</v>
       </c>
-      <c r="B26" s="27"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="23"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
       <c r="T26" s="24"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="65"/>
-      <c r="X26" s="63"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="26"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="62"/>
     </row>
-    <row r="27" spans="1:24">
-      <c r="A27" s="26">
+    <row r="27" ht="15.75" spans="1:24">
+      <c r="A27" s="25">
         <v>17</v>
       </c>
-      <c r="B27" s="27"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="23"/>
       <c r="D27" s="24"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
       <c r="T27" s="24"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-      <c r="W27" s="65"/>
-      <c r="X27" s="63"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="64"/>
+      <c r="X27" s="62"/>
     </row>
-    <row r="28" spans="1:24">
-      <c r="A28" s="26">
+    <row r="28" ht="15.75" spans="1:24">
+      <c r="A28" s="25">
         <v>18</v>
       </c>
-      <c r="B28" s="27"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="23"/>
       <c r="D28" s="24"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
       <c r="T28" s="24"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="65"/>
-      <c r="X28" s="63"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="62"/>
     </row>
-    <row r="29" spans="1:24">
-      <c r="A29" s="26">
+    <row r="29" ht="15.75" spans="1:24">
+      <c r="A29" s="25">
         <v>19</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="23"/>
       <c r="D29" s="24"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
       <c r="T29" s="24"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="65"/>
-      <c r="X29" s="63"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="26"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="62"/>
     </row>
-    <row r="30" spans="1:24">
-      <c r="A30" s="26">
+    <row r="30" ht="15.75" spans="1:24">
+      <c r="A30" s="25">
         <v>20</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="23"/>
       <c r="D30" s="24"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
       <c r="T30" s="24"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
-      <c r="W30" s="65"/>
-      <c r="X30" s="63"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="26"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="62"/>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31" t="str">
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30" t="str">
         <f t="shared" ref="U31:X31" si="0">IF(U11=" "," ",IF(MIN(U11:U30)=0," ",MIN(U11:U30)))</f>
         <v> </v>
       </c>
-      <c r="V31" s="31" t="str">
+      <c r="V31" s="30" t="str">
         <f t="shared" si="0"/>
         <v> </v>
       </c>
-      <c r="W31" s="31" t="str">
+      <c r="W31" s="30" t="str">
         <f t="shared" si="0"/>
         <v> </v>
       </c>
-      <c r="X31" s="66" t="str">
+      <c r="X31" s="65" t="str">
         <f t="shared" si="0"/>
         <v> </v>
       </c>
-      <c r="Y31" s="70"/>
+      <c r="Y31" s="69"/>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31" t="str">
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30" t="str">
         <f t="shared" ref="U32:X32" si="1">IF(U11=" "," ",IF(U31=" "," ",AVERAGE(U11:U30)))</f>
         <v> </v>
       </c>
-      <c r="V32" s="31" t="str">
+      <c r="V32" s="30" t="str">
         <f t="shared" si="1"/>
         <v> </v>
       </c>
-      <c r="W32" s="31" t="str">
+      <c r="W32" s="30" t="str">
         <f t="shared" si="1"/>
         <v> </v>
       </c>
-      <c r="X32" s="66" t="str">
+      <c r="X32" s="65" t="str">
         <f t="shared" si="1"/>
         <v> </v>
       </c>
-      <c r="Y32" s="70"/>
+      <c r="Y32" s="69"/>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31" t="str">
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30" t="str">
         <f t="shared" ref="U33:X33" si="2">IF(U11=" "," ",IF(U31=" "," ",MAX(U11:U30)))</f>
         <v> </v>
       </c>
-      <c r="V33" s="31" t="str">
+      <c r="V33" s="30" t="str">
         <f t="shared" si="2"/>
         <v> </v>
       </c>
-      <c r="W33" s="31" t="str">
+      <c r="W33" s="30" t="str">
         <f t="shared" si="2"/>
         <v> </v>
       </c>
-      <c r="X33" s="66" t="str">
+      <c r="X33" s="65" t="str">
         <f t="shared" si="2"/>
         <v> </v>
       </c>
-      <c r="Y33" s="70"/>
+      <c r="Y33" s="69"/>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31" t="str">
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30" t="str">
         <f t="shared" ref="U34:X34" si="3">IF(U11=" "," ",IF(U31=" "," ",STDEV(U11:U30)))</f>
         <v> </v>
       </c>
-      <c r="V34" s="31" t="str">
+      <c r="V34" s="30" t="str">
         <f t="shared" si="3"/>
         <v> </v>
       </c>
-      <c r="W34" s="31" t="str">
+      <c r="W34" s="30" t="str">
         <f t="shared" si="3"/>
         <v> </v>
       </c>
-      <c r="X34" s="66" t="str">
+      <c r="X34" s="65" t="str">
         <f t="shared" si="3"/>
         <v> </v>
       </c>
-      <c r="Y34" s="70"/>
+      <c r="Y34" s="69"/>
     </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="32" t="s">
+    <row r="35" ht="15.75" spans="1:25">
+      <c r="A35" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="67"/>
-      <c r="V35" s="67"/>
-      <c r="W35" s="67"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="70"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="66"/>
+      <c r="V35" s="66"/>
+      <c r="W35" s="66"/>
+      <c r="X35" s="67"/>
+      <c r="Y35" s="69"/>
     </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="34" t="s">
+    <row r="36" ht="15.75" spans="1:23">
+      <c r="A36" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="69"/>
-      <c r="V36" s="69"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="68"/>
+      <c r="V36" s="68"/>
       <c r="W36"/>
     </row>
     <row r="38" spans="21:22">
-      <c r="U38" s="70"/>
-      <c r="V38" s="70"/>
+      <c r="U38" s="69"/>
+      <c r="V38" s="69"/>
     </row>
     <row r="39" spans="22:22">
-      <c r="V39" s="70"/>
+      <c r="V39" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="70">
@@ -3920,82 +3920,6 @@
       <formula>160</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16;H22">
-    <cfRule type="cellIs" dxfId="0" priority="81" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="276" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16;J22">
-    <cfRule type="cellIs" dxfId="0" priority="18" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="17" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17;G19;G21">
-    <cfRule type="cellIs" dxfId="0" priority="12" stopIfTrue="1" operator="lessThan">
-      <formula>154</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" stopIfTrue="1" operator="lessThan">
-      <formula>160</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" stopIfTrue="1" operator="lessThan">
-      <formula>154</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" stopIfTrue="1" operator="lessThan">
-      <formula>160</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17;H19;H21">
-    <cfRule type="cellIs" dxfId="0" priority="16" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="14" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17;J19;J21">
-    <cfRule type="cellIs" dxfId="0" priority="4" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18;G20">
-    <cfRule type="cellIs" dxfId="0" priority="11" stopIfTrue="1" operator="lessThan">
-      <formula>154</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="9" stopIfTrue="1" operator="lessThan">
-      <formula>160</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" stopIfTrue="1" operator="lessThan">
-      <formula>154</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" stopIfTrue="1" operator="lessThan">
-      <formula>160</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18;H20">
-    <cfRule type="cellIs" dxfId="0" priority="15" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="13" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18;J20">
-    <cfRule type="cellIs" dxfId="0" priority="3" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
-      <formula>55</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="85" orientation="landscape"/>
